--- a/outputs/All_States_negative_prices.xlsx
+++ b/outputs/All_States_negative_prices.xlsx
@@ -1,17 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="NSW" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="QLD" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="VIC" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SA" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TAS" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="NSW" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="QLD" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="VIC" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="SA" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="TAS" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>

--- a/outputs/All_States_negative_prices.xlsx
+++ b/outputs/All_States_negative_prices.xlsx
@@ -444,7 +444,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J84"/>
+  <dimension ref="A1:J85"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -3333,6 +3333,40 @@
         <v>0</v>
       </c>
     </row>
+    <row r="85">
+      <c r="A85" s="2" t="inlineStr">
+        <is>
+          <t>Apr 2026</t>
+        </is>
+      </c>
+      <c r="B85" s="3" t="n">
+        <v>19.2</v>
+      </c>
+      <c r="C85" s="3" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="D85" s="3" t="n">
+        <v>0.49</v>
+      </c>
+      <c r="E85" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F85" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G85" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H85" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I85" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J85" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3344,7 +3378,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J84"/>
+  <dimension ref="A1:J85"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -6233,6 +6267,40 @@
         <v>0</v>
       </c>
     </row>
+    <row r="85">
+      <c r="A85" s="2" t="inlineStr">
+        <is>
+          <t>Apr 2026</t>
+        </is>
+      </c>
+      <c r="B85" s="3" t="n">
+        <v>39.06</v>
+      </c>
+      <c r="C85" s="3" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="D85" s="3" t="n">
+        <v>0.49</v>
+      </c>
+      <c r="E85" s="3" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="F85" s="3" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="G85" s="3" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="H85" s="3" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="I85" s="3" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="J85" s="3" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -6244,7 +6312,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J84"/>
+  <dimension ref="A1:J85"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -9133,6 +9201,40 @@
         <v>0.03</v>
       </c>
     </row>
+    <row r="85">
+      <c r="A85" s="2" t="inlineStr">
+        <is>
+          <t>Apr 2026</t>
+        </is>
+      </c>
+      <c r="B85" s="3" t="n">
+        <v>56.49</v>
+      </c>
+      <c r="C85" s="3" t="n">
+        <v>21.25</v>
+      </c>
+      <c r="D85" s="3" t="n">
+        <v>10.24</v>
+      </c>
+      <c r="E85" s="3" t="n">
+        <v>7.81</v>
+      </c>
+      <c r="F85" s="3" t="n">
+        <v>5.97</v>
+      </c>
+      <c r="G85" s="3" t="n">
+        <v>4.62</v>
+      </c>
+      <c r="H85" s="3" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="I85" s="3" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="J85" s="3" t="n">
+        <v>0.35</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -9144,7 +9246,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J84"/>
+  <dimension ref="A1:J85"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -12033,6 +12135,40 @@
         <v>11.53</v>
       </c>
     </row>
+    <row r="85">
+      <c r="A85" s="2" t="inlineStr">
+        <is>
+          <t>Apr 2026</t>
+        </is>
+      </c>
+      <c r="B85" s="3" t="n">
+        <v>54.17</v>
+      </c>
+      <c r="C85" s="3" t="n">
+        <v>18.23</v>
+      </c>
+      <c r="D85" s="3" t="n">
+        <v>6.98</v>
+      </c>
+      <c r="E85" s="3" t="n">
+        <v>6.18</v>
+      </c>
+      <c r="F85" s="3" t="n">
+        <v>5.66</v>
+      </c>
+      <c r="G85" s="3" t="n">
+        <v>4.62</v>
+      </c>
+      <c r="H85" s="3" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="I85" s="3" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="J85" s="3" t="n">
+        <v>1.46</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -12044,7 +12180,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J84"/>
+  <dimension ref="A1:J85"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -14933,6 +15069,40 @@
         <v>0</v>
       </c>
     </row>
+    <row r="85">
+      <c r="A85" s="2" t="inlineStr">
+        <is>
+          <t>Apr 2026</t>
+        </is>
+      </c>
+      <c r="B85" s="3" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="C85" s="3" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="D85" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E85" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F85" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G85" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H85" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I85" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J85" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
